--- a/StructureDefinition-access-eckm-condition.xlsx
+++ b/StructureDefinition-access-eckm-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-condition|0.7.0</t>
+    <t>https://globalalliantinc.com/access/StructureDefinition/access-condition|0.9.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -717,13 +717,13 @@
     <t>eCKM track diagnosis code</t>
   </si>
   <si>
-    <t>Diagnosis code for eCKM track conditions. SHOULD be from ACCESSeCKMDiagnosisVS (hypertension, dyslipidemia, prediabetes, obesity), but other ICD-10-CM codes are permitted.</t>
+    <t>Diagnosis code for eCKM track conditions. Values SHALL be from ACCESSeCKMDiagnosisVS (hypertension, dyslipidemia, prediabetes, obesity).</t>
   </si>
   <si>
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSeCKMDiagnosisVS|0.7.0</t>
+    <t>https://globalalliantinc.com/access/ValueSet/ACCESSeCKMDiagnosisVS|0.9.0</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/StructureDefinition-access-eckm-condition.xlsx
+++ b/StructureDefinition-access-eckm-condition.xlsx
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-eckm-condition</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-eckm-condition</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-condition|0.9.0</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -723,7 +723,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSeCKMDiagnosisVS|0.9.0</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.1</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/StructureDefinition-access-eckm-condition.xlsx
+++ b/StructureDefinition-access-eckm-condition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="438">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.1</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.6</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -373,9 +373,6 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
@@ -467,7 +464,7 @@
     <t>assertedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {condition-assertedDate|5.2.0}
+    <t xml:space="preserve">Extension {condition-assertedDate|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -653,6 +650,14 @@
     <t>(USCDI) problem-list-item | health-concern</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/condition-category"/&gt;
+    &lt;code value="problem-list-item"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
@@ -723,7 +728,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.1</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.6</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -2420,29 +2425,27 @@
       <c r="X6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -2477,14 +2480,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2503,16 +2506,16 @@
         <v>79</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2562,7 +2565,7 @@
         <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2586,7 +2589,7 @@
         <v>79</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -2597,14 +2600,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2623,16 +2626,16 @@
         <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2682,7 +2685,7 @@
         <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2706,7 +2709,7 @@
         <v>79</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -2717,10 +2720,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2743,13 +2746,13 @@
         <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2788,17 +2791,17 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2810,7 +2813,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>79</v>
@@ -2833,13 +2836,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -2861,16 +2864,16 @@
         <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2920,7 +2923,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2929,10 +2932,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>79</v>
@@ -2955,14 +2958,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2981,19 +2984,19 @@
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
@@ -3042,7 +3045,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3054,7 +3057,7 @@
         <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
@@ -3066,7 +3069,7 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>79</v>
@@ -3077,10 +3080,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3103,19 +3106,19 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -3164,7 +3167,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3179,19 +3182,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>79</v>
@@ -3199,10 +3202,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3225,16 +3228,16 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3260,11 +3263,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3282,7 +3285,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3291,25 +3294,25 @@
         <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3317,10 +3320,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3343,16 +3346,16 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3378,11 +3381,11 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3400,7 +3403,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3409,36 +3412,36 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>188</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3461,16 +3464,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3496,29 +3499,29 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3536,16 +3539,16 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3553,13 +3556,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>79</v>
@@ -3569,7 +3572,7 @@
         <v>91</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>92</v>
@@ -3581,16 +3584,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3601,7 +3604,7 @@
         <v>79</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>79</v>
@@ -3616,7 +3619,7 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y16" t="s" s="2">
         <v>203</v>
@@ -3640,7 +3643,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3658,16 +3661,16 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -3678,7 +3681,7 @@
         <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>206</v>
@@ -3703,7 +3706,7 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>207</v>
@@ -3712,7 +3715,7 @@
         <v>208</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O17" t="s" s="2">
         <v>209</v>
@@ -3740,7 +3743,7 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y17" t="s" s="2">
         <v>203</v>
@@ -3764,7 +3767,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3782,16 +3785,16 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3825,7 +3828,7 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>212</v>
@@ -3945,7 +3948,7 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>223</v>
@@ -3980,7 +3983,7 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
@@ -4162,7 +4165,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4181,7 +4184,7 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>240</v>
@@ -4190,7 +4193,7 @@
         <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4228,7 +4231,7 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC21" t="s" s="2">
         <v>242</v>
@@ -4237,7 +4240,7 @@
         <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>243</v>
@@ -4252,7 +4255,7 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
@@ -4357,7 +4360,7 @@
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>251</v>
@@ -4644,7 +4647,7 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4663,7 +4666,7 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>240</v>
@@ -4672,7 +4675,7 @@
         <v>241</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4710,7 +4713,7 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC25" t="s" s="2">
         <v>242</v>
@@ -4719,7 +4722,7 @@
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>243</v>
@@ -4734,7 +4737,7 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -5509,7 +5512,7 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>315</v>
@@ -6680,7 +6683,7 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6699,7 +6702,7 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>240</v>
@@ -6708,7 +6711,7 @@
         <v>241</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6770,7 +6773,7 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6819,7 +6822,7 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>388</v>
@@ -6828,10 +6831,10 @@
         <v>389</v>
       </c>
       <c r="N43" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6892,7 +6895,7 @@
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -6904,7 +6907,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6941,7 +6944,7 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>392</v>
@@ -7019,7 +7022,7 @@
         <v>397</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>230</v>
@@ -7177,7 +7180,7 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>404</v>
@@ -7514,7 +7517,7 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7533,7 +7536,7 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>240</v>
@@ -7542,7 +7545,7 @@
         <v>241</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7604,7 +7607,7 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7653,7 +7656,7 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>388</v>
@@ -7662,10 +7665,10 @@
         <v>389</v>
       </c>
       <c r="N50" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7726,7 +7729,7 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -7738,7 +7741,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7775,7 +7778,7 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>419</v>
@@ -7850,7 +7853,7 @@
         <v>424</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-access-eckm-condition.xlsx
+++ b/StructureDefinition-access-eckm-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.8</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -464,7 +464,7 @@
     <t>assertedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {condition-assertedDate|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {condition-assertedDate|5.2.0}
 </t>
   </si>
   <si>
@@ -728,7 +728,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.8</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/StructureDefinition-access-eckm-condition.xlsx
+++ b/StructureDefinition-access-eckm-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.11</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -728,7 +728,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.11</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/StructureDefinition-access-eckm-condition.xlsx
+++ b/StructureDefinition-access-eckm-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.12</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -728,7 +728,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS|0.9.12</t>
   </si>
   <si>
     <t>Event.code</t>
